--- a/administrative_forms/011_fire_alarm_inspection_checklist_form--administrative_forms.xlsx
+++ b/administrative_forms/011_fire_alarm_inspection_checklist_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>main_page_1</t>
+          <t>fire_alarm_system</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>main_page_2</t>
+          <t>system_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>main_page_2_1</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>System Location</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>main_page_3</t>
+          <t>inspectors_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>main_page_4</t>
+          <t>fire_officer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>main_page_5</t>
+          <t>inspector_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inspectors Name</t>
+          <t>Inspector Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>main_page_6</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>main_page_7</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>main_page_8</t>
+          <t>time_zone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -738,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>main_page_9</t>
+          <t>inspector_signature</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>main_page_10</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>main_page_11</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -807,7 +807,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>main_page_12</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>main_page_13</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>main_page_14</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>main_page_15</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>main_page_16</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -923,167 +923,6 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>main_page_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Company Name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>main_page_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>main_page_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Company Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>main_page_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>main_page_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>main_page_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Time Zone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>main_page_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Inspector Signature</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1101,9 +940,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +965,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>main_page_1_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'value-1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'value-1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>main_page_1_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'value-2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'value-2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>main_page_1_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'value-3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'value-3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>main_page_2_1_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'location_1',_'value':_'location-1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Location 1', 'value': 'location-1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>main_page_2_1_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'location_2',_'value':_'location-2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Location 2', 'value': 'location-2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>main_page_2_1_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'location_3',_'value':_'location-3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Location 3', 'value': 'location-3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
